--- a/data/trans_orig/P17G-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P17G-Clase-trans_orig.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>6726</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10129</t>
+          <t>9602</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18607</t>
+          <t>19153</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7209</t>
+          <t>7587</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>7227</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22590</t>
+          <t>21750</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3459</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13630</t>
+          <t>13459</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3800</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14256</t>
+          <t>14534</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>9230</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24592</t>
+          <t>23911</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49522</t>
+          <t>51025</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>66134</t>
+          <t>66461</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56051</t>
+          <t>55580</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>68300</t>
+          <t>68337</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>110358</t>
+          <t>111408</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>131823</t>
+          <t>131168</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,03%</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6379</t>
+          <t>5672</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10314</t>
+          <t>10831</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13709</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>6036</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20787</t>
+          <t>20563</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9354</t>
+          <t>8853</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>974</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10989</t>
+          <t>10289</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49625</t>
+          <t>50081</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59642</t>
+          <t>59656</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>79514</t>
+          <t>79398</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>92719</t>
+          <t>93180</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>133408</t>
+          <t>134663</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>150691</t>
+          <t>150862</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>884</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7357</t>
+          <t>8459</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>879</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6895</t>
+          <t>7573</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10175</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>870</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>14221</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>821</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9568</t>
+          <t>9370</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1411</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11382</t>
+          <t>12873</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>98389</t>
+          <t>98950</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>111560</t>
+          <t>111632</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48713</t>
+          <t>48754</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58260</t>
+          <t>58072</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>152883</t>
+          <t>152050</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>167807</t>
+          <t>167625</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12078</t>
+          <t>12425</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11015</t>
+          <t>10619</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5857</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>18246</t>
+          <t>19955</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2773</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16693</t>
+          <t>16529</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14747</t>
+          <t>14956</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7396</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24260</t>
+          <t>25310</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10025</t>
+          <t>10975</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>966</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8002</t>
+          <t>9661</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2966</t>
+          <t>3571</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14483</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>260700</t>
+          <t>260495</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>276891</t>
+          <t>276852</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>198427</t>
+          <t>197090</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>213625</t>
+          <t>213339</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>464218</t>
+          <t>462881</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>487319</t>
+          <t>487654</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>837</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>922</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>9259</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -3692,7 +3692,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5137</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>6212</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>826</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7274</t>
+          <t>7500</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9883</t>
+          <t>11347</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9803</t>
+          <t>9122</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>72256</t>
+          <t>71600</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>79524</t>
+          <t>79493</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>187141</t>
+          <t>187033</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>197731</t>
+          <t>198197</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>263696</t>
+          <t>262820</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>276217</t>
+          <t>276039</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4123,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4996</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -4404,12 +4404,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3683</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>16707</t>
+          <t>15695</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>16231</t>
+          <t>16390</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>4457</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3938</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>15162</t>
+          <t>15586</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4532,12 +4532,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>15565</t>
+          <t>16787</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4567,12 +4567,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>20905</t>
+          <t>20604</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>365412</t>
+          <t>367100</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>383388</t>
+          <t>383774</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>390833</t>
+          <t>390427</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>407471</t>
+          <t>407553</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -4938,12 +4938,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>22977</t>
+          <t>22857</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4953,12 +4953,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>17098</t>
+          <t>17518</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>16578</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>35823</t>
+          <t>36941</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5023,12 +5023,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -5051,12 +5051,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>19639</t>
+          <t>20257</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>42027</t>
+          <t>45440</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>19124</t>
+          <t>19787</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>41817</t>
+          <t>42258</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>44544</t>
+          <t>43861</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>77407</t>
+          <t>76945</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -5164,12 +5164,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>10358</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>27169</t>
+          <t>26544</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>16555</t>
+          <t>16984</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>37560</t>
+          <t>37494</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>31051</t>
+          <t>31597</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>57936</t>
+          <t>57678</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -5277,12 +5277,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>575313</t>
+          <t>574171</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>604940</t>
+          <t>605284</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5292,12 +5292,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>964140</t>
+          <t>965119</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>997163</t>
+          <t>997968</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1551538</t>
+          <t>1552686</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1593972</t>
+          <t>1596425</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,84%</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9043</t>
+          <t>9135</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8903</t>
+          <t>8947</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11549</t>
+          <t>11602</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>915</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>8525</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15462</t>
+          <t>14877</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -6080,12 +6080,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16820</t>
+          <t>17924</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6095,12 +6095,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6190</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20259</t>
+          <t>18793</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11482</t>
+          <t>11997</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29951</t>
+          <t>30394</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53919</t>
+          <t>53096</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67770</t>
+          <t>68009</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6208,12 +6208,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54403</t>
+          <t>54389</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>69323</t>
+          <t>69681</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>113199</t>
+          <t>112668</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>133172</t>
+          <t>134228</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,88%</t>
         </is>
       </c>
     </row>
@@ -6541,7 +6541,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6050</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -6649,12 +6649,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>4353</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17439</t>
+          <t>17115</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7034</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19673</t>
+          <t>19508</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,48%</t>
         </is>
       </c>
     </row>
@@ -6762,12 +6762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5760</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18963</t>
+          <t>19279</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6777,12 +6777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2818</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15719</t>
+          <t>16479</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6812,12 +6812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10804</t>
+          <t>11171</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29146</t>
+          <t>29197</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -6875,12 +6875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64604</t>
+          <t>63438</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>81948</t>
+          <t>81677</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6890,12 +6890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>73125</t>
+          <t>72101</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>87180</t>
+          <t>86668</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>143286</t>
+          <t>143471</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>165846</t>
+          <t>165044</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,64%</t>
         </is>
       </c>
     </row>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5627</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>6719</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7928</t>
+          <t>8951</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10347</t>
+          <t>10053</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -7449,7 +7449,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>5531</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>6028</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>146151</t>
+          <t>146097</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>152967</t>
+          <t>152981</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>80119</t>
+          <t>79819</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>89127</t>
+          <t>89088</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>230009</t>
+          <t>229886</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>241922</t>
+          <t>241119</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1790</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12311</t>
+          <t>12603</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10683</t>
+          <t>12878</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -8018,7 +8018,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6661</t>
+          <t>6228</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4765</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>912</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4825</t>
+          <t>4858</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4464</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -8239,12 +8239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>281546</t>
+          <t>280577</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>292686</t>
+          <t>292684</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>240623</t>
+          <t>240595</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>526772</t>
+          <t>526423</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>538340</t>
+          <t>538962</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>4639</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5841</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6494</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7835</t>
+          <t>7356</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>103918</t>
+          <t>103552</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>268605</t>
+          <t>268568</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>373541</t>
+          <t>374882</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>382363</t>
+          <t>382369</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -9131,7 +9131,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6426</t>
+          <t>6124</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>14858</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>17924</t>
+          <t>18211</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9490,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>991</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>10418</t>
+          <t>10863</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>9824</t>
+          <t>9703</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>3728</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>15109</t>
+          <t>16098</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>24681</t>
+          <t>23857</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>35325</t>
+          <t>35348</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>330965</t>
+          <t>332124</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>345857</t>
+          <t>345353</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>360893</t>
+          <t>360098</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>378853</t>
+          <t>378661</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>5232</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -9946,12 +9946,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>2941</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>14348</t>
+          <t>14359</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>9637</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>4674</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>19258</t>
+          <t>19257</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>11838</t>
+          <t>12503</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>29836</t>
+          <t>30211</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>11930</t>
+          <t>12206</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>30262</t>
+          <t>29238</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>27814</t>
+          <t>27566</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>52821</t>
+          <t>51540</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>14974</t>
+          <t>15764</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>39082</t>
+          <t>37852</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>15579</t>
+          <t>15205</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>36586</t>
+          <t>36405</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>34356</t>
+          <t>35786</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>65745</t>
+          <t>66481</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -10285,12 +10285,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>697696</t>
+          <t>697117</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>727819</t>
+          <t>727412</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1072622</t>
+          <t>1073880</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1101311</t>
+          <t>1102398</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1781115</t>
+          <t>1780174</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1821282</t>
+          <t>1821804</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>
@@ -10862,12 +10862,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>970</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8397</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10877,12 +10877,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10932,12 +10932,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>979</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>9218</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10947,12 +10947,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -10975,12 +10975,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>962</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>8257</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10990,12 +10990,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4865</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11045,12 +11045,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>998</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -11088,12 +11088,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10563</t>
+          <t>10471</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26912</t>
+          <t>27726</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11123,12 +11123,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9160</t>
+          <t>9007</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24784</t>
+          <t>23815</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11138,12 +11138,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11158,12 +11158,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22891</t>
+          <t>22173</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45890</t>
+          <t>44640</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -11201,12 +11201,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68768</t>
+          <t>69480</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>86826</t>
+          <t>86932</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11216,12 +11216,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11236,12 +11236,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68754</t>
+          <t>69938</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>85107</t>
+          <t>84924</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11251,12 +11251,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11271,12 +11271,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>143897</t>
+          <t>143876</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>168242</t>
+          <t>168828</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11286,12 +11286,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,49%</t>
         </is>
       </c>
     </row>
@@ -11584,7 +11584,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11619,7 +11619,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6449</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>850</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11672,12 +11672,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6677</t>
+          <t>8530</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11727,12 +11727,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10971</t>
+          <t>10551</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -11770,12 +11770,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7783</t>
+          <t>7428</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21440</t>
+          <t>21965</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11785,12 +11785,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11805,12 +11805,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11659</t>
+          <t>11832</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11840,12 +11840,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12338</t>
+          <t>12063</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29059</t>
+          <t>28784</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -11883,12 +11883,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>67910</t>
+          <t>67948</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>82599</t>
+          <t>82996</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11898,12 +11898,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11918,12 +11918,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76788</t>
+          <t>76558</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>88567</t>
+          <t>88651</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11953,12 +11953,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>149339</t>
+          <t>149601</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>168680</t>
+          <t>168663</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11968,12 +11968,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,59%</t>
         </is>
       </c>
     </row>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>5820</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11342</t>
+          <t>12411</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12354,12 +12354,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12379,7 +12379,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4729</t>
+          <t>5028</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12394,7 +12394,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12409,12 +12409,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2079</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12742</t>
+          <t>13935</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6616</t>
+          <t>6689</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>7133</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12522,12 +12522,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>954</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9867</t>
+          <t>9506</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12537,12 +12537,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -12565,12 +12565,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>138453</t>
+          <t>137749</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>150215</t>
+          <t>150360</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51846</t>
+          <t>52375</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59673</t>
+          <t>60596</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12635,12 +12635,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>194064</t>
+          <t>193944</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>208471</t>
+          <t>208905</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12650,12 +12650,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>4929</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12870,7 +12870,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12885,7 +12885,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -12908,12 +12908,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8863</t>
+          <t>9734</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12983,7 +12983,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9581</t>
+          <t>9590</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12260</t>
+          <t>12003</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>14488</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13091,12 +13091,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5440</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20959</t>
+          <t>20823</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13106,12 +13106,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -13134,12 +13134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2188</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13258</t>
+          <t>14008</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13149,12 +13149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13169,12 +13169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11443</t>
+          <t>12771</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13184,12 +13184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13204,12 +13204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20118</t>
+          <t>21768</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13219,12 +13219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>263956</t>
+          <t>264107</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>281039</t>
+          <t>280890</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13262,12 +13262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13282,12 +13282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>244703</t>
+          <t>243785</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>258588</t>
+          <t>258807</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13297,12 +13297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>514608</t>
+          <t>512853</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>535913</t>
+          <t>535728</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13332,12 +13332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -13595,7 +13595,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13610,7 +13610,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13625,12 +13625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>878</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>8628</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13640,12 +13640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13660,12 +13660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>892</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9878</t>
+          <t>9896</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13675,12 +13675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -13708,7 +13708,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13723,7 +13723,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13738,12 +13738,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9859</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13758,7 +13758,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13773,12 +13773,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>12326</t>
+          <t>12013</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -13816,12 +13816,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>9765</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13836,7 +13836,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13851,12 +13851,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>966</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11185</t>
+          <t>10677</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13871,7 +13871,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13886,12 +13886,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t>3219</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>15150</t>
+          <t>15870</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -13929,12 +13929,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>150202</t>
+          <t>150064</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>160772</t>
+          <t>159854</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13944,12 +13944,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13964,12 +13964,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>242921</t>
+          <t>242393</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>256406</t>
+          <t>256862</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13979,12 +13979,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13999,12 +13999,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>398330</t>
+          <t>398104</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>414069</t>
+          <t>415163</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -14139,7 +14139,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -14277,7 +14277,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>6675</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14292,7 +14292,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14347,7 +14347,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6732</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14362,7 +14362,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -14420,12 +14420,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>936</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10646</t>
+          <t>10951</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14440,7 +14440,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14455,12 +14455,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>943</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>10709</t>
+          <t>11343</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -14498,12 +14498,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>856</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>7331</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14513,12 +14513,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14533,12 +14533,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>6914</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>23833</t>
+          <t>24403</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14548,12 +14548,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14568,12 +14568,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>9351</t>
+          <t>9258</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>27742</t>
+          <t>27587</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14583,12 +14583,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -14611,12 +14611,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>32894</t>
+          <t>33911</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>41795</t>
+          <t>41857</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14626,12 +14626,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14646,12 +14646,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>332926</t>
+          <t>334624</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>352444</t>
+          <t>353114</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14661,12 +14661,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14681,12 +14681,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>372289</t>
+          <t>371604</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>391915</t>
+          <t>391737</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14696,12 +14696,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -14846,7 +14846,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>5669</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14861,7 +14861,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>6080</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14931,7 +14931,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -14954,12 +14954,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>5838</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>18262</t>
+          <t>18624</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14974,7 +14974,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14989,12 +14989,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>10682</t>
+          <t>10874</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15009,7 +15009,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15024,12 +15024,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>8753</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>23748</t>
+          <t>25406</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15039,12 +15039,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -15067,12 +15067,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>9160</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>26755</t>
+          <t>25541</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15087,7 +15087,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15102,12 +15102,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>11557</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>30664</t>
+          <t>29640</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15117,12 +15117,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15137,12 +15137,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>23445</t>
+          <t>23667</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>48783</t>
+          <t>48273</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15152,12 +15152,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -15180,12 +15180,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>32771</t>
+          <t>32182</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>60295</t>
+          <t>60616</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15195,12 +15195,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15215,12 +15215,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>34480</t>
+          <t>34739</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>62674</t>
+          <t>61633</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15230,12 +15230,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15250,12 +15250,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>73001</t>
+          <t>73810</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>113932</t>
+          <t>113220</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15265,12 +15265,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -15293,12 +15293,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>753571</t>
+          <t>750704</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>786816</t>
+          <t>786560</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15308,12 +15308,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15328,12 +15328,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1048900</t>
+          <t>1050905</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1083559</t>
+          <t>1082945</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15343,12 +15343,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15363,12 +15363,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1814372</t>
+          <t>1812027</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1862679</t>
+          <t>1859340</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15378,12 +15378,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -15787,7 +15787,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>675</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -15797,12 +15797,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3693</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -15812,7 +15812,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -15822,7 +15822,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>675</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -15832,7 +15832,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -15847,7 +15847,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -15865,17 +15865,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>681</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6597</t>
+          <t>6762</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -15885,12 +15885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -15900,32 +15900,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>536</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -15935,32 +15935,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>1608</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8378</t>
+          <t>9241</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -15978,32 +15978,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16043</t>
+          <t>16609</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9574</t>
+          <t>9932</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25949</t>
+          <t>25840</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -16013,32 +16013,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>16374</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9180</t>
+          <t>11160</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20852</t>
+          <t>24262</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -16048,32 +16048,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>30464</t>
+          <t>32982</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22367</t>
+          <t>22731</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42464</t>
+          <t>44819</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -16091,32 +16091,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10923</t>
+          <t>12010</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>6808</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19651</t>
+          <t>20701</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -16126,32 +16126,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12820</t>
+          <t>13001</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8444</t>
+          <t>8092</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19340</t>
+          <t>20096</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -16161,32 +16161,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>23742</t>
+          <t>25012</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16419</t>
+          <t>17420</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33679</t>
+          <t>34814</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -16204,32 +16204,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>91131</t>
+          <t>100442</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80380</t>
+          <t>89754</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>99937</t>
+          <t>108904</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -16239,32 +16239,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>77723</t>
+          <t>88432</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>70428</t>
+          <t>79578</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84707</t>
+          <t>96104</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -16274,32 +16274,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>168854</t>
+          <t>188874</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>155429</t>
+          <t>174735</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>180077</t>
+          <t>201477</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>80,0%</t>
         </is>
       </c>
     </row>
@@ -16317,17 +16317,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>120285</t>
+          <t>131451</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>120285</t>
+          <t>131451</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>120285</t>
+          <t>131451</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -16352,17 +16352,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>107399</t>
+          <t>120381</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>107399</t>
+          <t>120381</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>107399</t>
+          <t>120381</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -16387,17 +16387,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>227684</t>
+          <t>251832</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>227684</t>
+          <t>251832</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>227684</t>
+          <t>251832</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -16547,7 +16547,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2367</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -16557,12 +16557,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -16572,7 +16572,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -16582,7 +16582,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>632</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -16592,12 +16592,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -16617,32 +16617,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>630</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8308</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -16660,102 +16660,102 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6074</t>
+          <t>7443</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>3695</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>15173</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7,62%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>15,53%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>11463</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>6776</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>18507</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>11,49%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>6,79%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>18,55%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>18906</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
           <t>12501</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,68%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>13,74%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>10526</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>6200</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>16707</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>11,64%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>6,85%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>18,47%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>16601</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>10886</t>
-        </is>
-      </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>24961</t>
+          <t>28394</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -16773,32 +16773,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10251</t>
+          <t>10808</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16568</t>
+          <t>17142</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -16808,32 +16808,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8010</t>
+          <t>8995</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>14572</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -16843,32 +16843,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>18261</t>
+          <t>19803</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11269</t>
+          <t>13064</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25931</t>
+          <t>27962</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -16886,32 +16886,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>72281</t>
+          <t>77083</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64496</t>
+          <t>68212</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>78753</t>
+          <t>84492</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -16921,32 +16921,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>71305</t>
+          <t>78705</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>64425</t>
+          <t>70577</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76953</t>
+          <t>84960</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -16956,32 +16956,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>143586</t>
+          <t>155788</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>132905</t>
+          <t>142899</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>152925</t>
+          <t>164887</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>83,49%</t>
         </is>
       </c>
     </row>
@@ -16999,17 +16999,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>90960</t>
+          <t>97702</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>90960</t>
+          <t>97702</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>90960</t>
+          <t>97702</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -17034,17 +17034,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>90469</t>
+          <t>99795</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>90469</t>
+          <t>99795</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>90469</t>
+          <t>99795</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -17069,17 +17069,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>181429</t>
+          <t>197497</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>181429</t>
+          <t>197497</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>181429</t>
+          <t>197497</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -17229,7 +17229,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -17239,12 +17239,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4594</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -17254,7 +17254,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -17299,7 +17299,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -17309,12 +17309,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>5728</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -17377,32 +17377,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>477</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -17412,32 +17412,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>481</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -17455,7 +17455,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -17465,12 +17465,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>6208</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -17490,32 +17490,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>690</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -17525,32 +17525,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>4594</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1426</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8303</t>
+          <t>9469</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -17568,32 +17568,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>84503</t>
+          <t>94049</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>80665</t>
+          <t>88541</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>86302</t>
+          <t>96211</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -17603,32 +17603,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>43390</t>
+          <t>48970</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39473</t>
+          <t>44807</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45938</t>
+          <t>51932</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -17638,32 +17638,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>127893</t>
+          <t>143019</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>122608</t>
+          <t>136906</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>130989</t>
+          <t>146828</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -17681,17 +17681,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>86471</t>
+          <t>97009</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>86471</t>
+          <t>97009</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>86471</t>
+          <t>97009</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -17716,17 +17716,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>47774</t>
+          <t>53623</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>47774</t>
+          <t>53623</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>47774</t>
+          <t>53623</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -17751,17 +17751,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>134245</t>
+          <t>150632</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>134245</t>
+          <t>150632</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>134245</t>
+          <t>150632</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -17833,7 +17833,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>703</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -17843,12 +17843,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -17858,7 +17858,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -17868,7 +17868,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>703</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -17878,12 +17878,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -17893,7 +17893,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -17911,7 +17911,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>2697</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -17921,12 +17921,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>9449</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -17936,7 +17936,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -17946,32 +17946,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>181</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4637</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -17981,32 +17981,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7403</t>
+          <t>10068</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -18024,32 +18024,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7612</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16712</t>
+          <t>19634</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -18059,32 +18059,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>7755</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13037</t>
+          <t>14283</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -18094,32 +18094,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>14195</t>
+          <t>15367</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7707</t>
+          <t>8610</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24374</t>
+          <t>26373</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -18137,32 +18137,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3725</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>918</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10612</t>
+          <t>10710</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -18172,7 +18172,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -18182,12 +18182,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4134</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -18197,7 +18197,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -18207,32 +18207,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11656</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -18250,32 +18250,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>205140</t>
+          <t>216985</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>195687</t>
+          <t>205821</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>211595</t>
+          <t>223954</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -18285,32 +18285,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>179798</t>
+          <t>204947</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>172926</t>
+          <t>197566</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>184699</t>
+          <t>210332</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -18320,32 +18320,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>384937</t>
+          <t>421932</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>372991</t>
+          <t>410108</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>393143</t>
+          <t>431455</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -18363,17 +18363,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>217315</t>
+          <t>231160</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>217315</t>
+          <t>231160</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>217315</t>
+          <t>231160</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -18398,17 +18398,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>190368</t>
+          <t>216538</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>190368</t>
+          <t>216538</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>190368</t>
+          <t>216538</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -18433,17 +18433,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>407682</t>
+          <t>447698</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>407682</t>
+          <t>447698</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>407682</t>
+          <t>447698</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -18628,32 +18628,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>735</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6898</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -18663,32 +18663,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>728</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7130</t>
+          <t>7695</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -18741,32 +18741,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10352</t>
+          <t>9870</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -18776,32 +18776,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2745</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>10120</t>
+          <t>10256</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -18819,7 +18819,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>802</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -18829,12 +18829,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5823</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -18854,7 +18854,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -18864,12 +18864,12 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -18879,7 +18879,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -18889,32 +18889,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>563</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6877</t>
+          <t>5585</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -18932,27 +18932,27 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>88092</t>
+          <t>95149</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>83183</t>
+          <t>92608</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>89006</t>
+          <t>95951</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -18967,32 +18967,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>259698</t>
+          <t>208775</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>253146</t>
+          <t>202889</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>265262</t>
+          <t>212908</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -19002,32 +19002,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>347791</t>
+          <t>303925</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>341082</t>
+          <t>298192</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>353375</t>
+          <t>308285</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -19045,17 +19045,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>89006</t>
+          <t>95951</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>89006</t>
+          <t>95951</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>89006</t>
+          <t>95951</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -19080,17 +19080,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>268680</t>
+          <t>218140</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>268680</t>
+          <t>218140</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>268680</t>
+          <t>218140</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -19115,17 +19115,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>357686</t>
+          <t>314091</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>357686</t>
+          <t>314091</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>357686</t>
+          <t>314091</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -19147,7 +19147,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -19388,7 +19388,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -19398,12 +19398,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>14060</t>
+          <t>12695</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -19413,7 +19413,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -19423,32 +19423,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>5864</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>14037</t>
+          <t>14243</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -19458,32 +19458,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>8942</t>
+          <t>8922</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>20681</t>
+          <t>20112</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -19536,32 +19536,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5674</t>
+          <t>6083</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2443</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10039</t>
+          <t>11040</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -19571,32 +19571,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>5674</t>
+          <t>6083</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>10669</t>
+          <t>11216</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -19614,27 +19614,27 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>20011</t>
+          <t>18357</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>9229</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>23289</t>
+          <t>21416</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -19649,32 +19649,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>161061</t>
+          <t>182742</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>152754</t>
+          <t>174863</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>165597</t>
+          <t>187954</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -19684,32 +19684,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>181072</t>
+          <t>201099</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>169974</t>
+          <t>190415</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>187838</t>
+          <t>207664</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -19727,17 +19727,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>23289</t>
+          <t>21416</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>23289</t>
+          <t>21416</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>23289</t>
+          <t>21416</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -19762,17 +19762,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>172399</t>
+          <t>194689</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>172399</t>
+          <t>194689</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>172399</t>
+          <t>194689</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -19797,17 +19797,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>195688</t>
+          <t>216105</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>195688</t>
+          <t>216105</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>195688</t>
+          <t>216105</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -19879,7 +19879,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -19889,7 +19889,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -19914,7 +19914,7 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
@@ -19924,7 +19924,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -19939,7 +19939,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -19957,32 +19957,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>13609</t>
+          <t>16877</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -19992,32 +19992,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>6637</t>
+          <t>7082</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>12399</t>
+          <t>13000</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -20027,32 +20027,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>13399</t>
+          <t>15661</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>8275</t>
+          <t>10048</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>22209</t>
+          <t>26203</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -20070,32 +20070,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>32671</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>21972</t>
+          <t>23858</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>49236</t>
+          <t>50941</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -20105,32 +20105,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>44688</t>
+          <t>48858</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>31102</t>
+          <t>37420</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>58491</t>
+          <t>62467</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -20140,32 +20140,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>77358</t>
+          <t>83581</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>59610</t>
+          <t>66293</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>98140</t>
+          <t>102210</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -20183,32 +20183,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>26735</t>
+          <t>29321</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>19248</t>
+          <t>20112</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>39795</t>
+          <t>42196</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -20218,32 +20218,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>31448</t>
+          <t>33278</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>20923</t>
+          <t>25675</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>42520</t>
+          <t>43207</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -20253,32 +20253,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>58183</t>
+          <t>62598</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>45037</t>
+          <t>50596</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>74160</t>
+          <t>79378</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -20296,32 +20296,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>561158</t>
+          <t>602067</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>542927</t>
+          <t>582154</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>576786</t>
+          <t>617884</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -20331,32 +20331,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>792974</t>
+          <t>812571</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>775752</t>
+          <t>796345</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>815366</t>
+          <t>827808</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -20366,32 +20366,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>1354133</t>
+          <t>1414638</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1329068</t>
+          <t>1388095</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1378558</t>
+          <t>1437715</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,12%</t>
         </is>
       </c>
     </row>
@@ -20409,17 +20409,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>627326</t>
+          <t>674690</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>627326</t>
+          <t>674690</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>627326</t>
+          <t>674690</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -20444,17 +20444,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>877089</t>
+          <t>903166</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>877089</t>
+          <t>903166</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>877089</t>
+          <t>903166</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -20479,17 +20479,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1504415</t>
+          <t>1577856</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1504415</t>
+          <t>1577856</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1504415</t>
+          <t>1577856</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
